--- a/exports/PAYTM_full_report.xlsx
+++ b/exports/PAYTM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>0.51</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44571.38541666666</v>
+        <v>44571.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>1182.8</v>
+        <v>1159</v>
       </c>
       <c r="I2" t="n">
         <v>1176.75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-2.01</v>
       </c>
       <c r="L2" t="n">
-        <v>0.13</v>
+        <v>2.52</v>
       </c>
       <c r="M2" t="n">
         <v>0.16</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.83</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44655.38541666666</v>
+        <v>44655.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>601.3</v>
+        <v>609.5</v>
       </c>
       <c r="I3" t="n">
         <v>603.0961255673958</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>83.83333333333333</v>
+        <v>84</v>
       </c>
       <c r="K3" t="n">
-        <v>48.12</v>
+        <v>47.41</v>
       </c>
       <c r="L3" t="n">
         <v>4.83</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>13.33</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>626.5</v>
+        <v>604.9</v>
       </c>
       <c r="I4" t="n">
         <v>618.973827105925</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>2.79</v>
+        <v>-0.75</v>
       </c>
       <c r="L4" t="n">
         <v>2.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.61</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.49</v>
+        <v>4.41</v>
       </c>
       <c r="O4" t="n">
         <v>6.93</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.72</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44697.38541666666</v>
+        <v>44697.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>558.5</v>
+        <v>590</v>
       </c>
       <c r="I5" t="n">
         <v>571.7738529557773</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>7.67</v>
+        <v>2.46</v>
       </c>
       <c r="L5" t="n">
         <v>2.93</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.16</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>597</v>
+        <v>585.75</v>
       </c>
       <c r="I6" t="n">
         <v>590.6349732575643</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>25</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>1.19</v>
+        <v>-0.72</v>
       </c>
       <c r="L6" t="n">
         <v>6.78</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>9.09</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44729.38541666666</v>
+        <v>44729.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>619.3</v>
+        <v>646.3</v>
       </c>
       <c r="I7" t="n">
         <v>631.5328432107653</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.73</v>
+        <v>-10.34</v>
       </c>
       <c r="L7" t="n">
-        <v>10.11</v>
+        <v>10.63</v>
       </c>
       <c r="M7" t="n">
         <v>1.85</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.22</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44743.55208333334</v>
+        <v>44746.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>657.7</v>
+        <v>638.45</v>
       </c>
       <c r="I8" t="n">
         <v>651.2272596131692</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>1.76</v>
+        <v>-1.21</v>
       </c>
       <c r="L8" t="n">
         <v>5.55</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>11.73</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44750.55208333334</v>
+        <v>44753.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>699.1</v>
+        <v>707.95</v>
       </c>
       <c r="I9" t="n">
         <v>702.958079053711</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.5</v>
+        <v>-10.89</v>
       </c>
       <c r="L9" t="n">
-        <v>10.49</v>
+        <v>12.62</v>
       </c>
       <c r="M9" t="n">
         <v>1.27</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>7.61</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>753</v>
+        <v>692</v>
       </c>
       <c r="I10" t="n">
         <v>707.3897301127004</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>6.36</v>
+        <v>-2.25</v>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>4.14</v>
       </c>
       <c r="M10" t="n">
         <v>0.42</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>13.01</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44776.38541666666</v>
+        <v>44776.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>757.5</v>
+        <v>801.5</v>
       </c>
       <c r="I11" t="n">
         <v>762.1248267069828</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.470000000000001</v>
+        <v>-15.82</v>
       </c>
       <c r="L11" t="n">
-        <v>11.15</v>
+        <v>17.53</v>
       </c>
       <c r="M11" t="n">
         <v>1.12</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>10.86</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44799.55208333334</v>
+        <v>44802.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>763.55</v>
+        <v>736.4</v>
       </c>
       <c r="I12" t="n">
         <v>761.0653374156136</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.73</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>5.74</v>
+        <v>8.32</v>
       </c>
       <c r="M12" t="n">
-        <v>0.95</v>
+        <v>2.17</v>
       </c>
       <c r="N12" t="n">
-        <v>4.59</v>
+        <v>4.66</v>
       </c>
       <c r="O12" t="n">
         <v>6.54</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.77</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>674.35</v>
+        <v>689.1</v>
       </c>
       <c r="I13" t="n">
         <v>681.7771673391746</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K13" t="n">
-        <v>8.43</v>
+        <v>6.42</v>
       </c>
       <c r="L13" t="n">
         <v>1.58</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.31</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44848.38541666666</v>
+        <v>44848.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>686.35</v>
+        <v>677</v>
       </c>
       <c r="I14" t="n">
         <v>682.7131554348794</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4</v>
+        <v>-1.76</v>
       </c>
       <c r="L14" t="n">
         <v>1.77</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.65</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44896.55208333334</v>
+        <v>44897.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>500.8</v>
+        <v>525.95</v>
       </c>
       <c r="I15" t="n">
         <v>508.7913003646983</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>26.03</v>
+        <v>22.31</v>
       </c>
       <c r="L15" t="n">
         <v>1.77</v>
@@ -1296,7 +1475,7 @@
         <v>2.91</v>
       </c>
       <c r="N15" t="n">
-        <v>5.86</v>
+        <v>7.76</v>
       </c>
       <c r="O15" t="n">
         <v>-1.31</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>12.03</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>506.05</v>
+        <v>483.5</v>
       </c>
       <c r="I16" t="n">
         <v>498.7504609837274</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.78</v>
+        <v>-8.07</v>
       </c>
       <c r="L16" t="n">
-        <v>3.98</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>3.09</v>
+        <v>6.14</v>
       </c>
       <c r="O16" t="n">
         <v>7.76</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>8.65</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44922.55208333334</v>
+        <v>44923.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>513</v>
+        <v>529.8</v>
       </c>
       <c r="I17" t="n">
         <v>515.1410150437189</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.1</v>
+        <v>-9.58</v>
       </c>
       <c r="L17" t="n">
-        <v>7.03</v>
+        <v>12.04</v>
       </c>
       <c r="M17" t="n">
         <v>0.84</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.65</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44937.55208333334</v>
+        <v>44938.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>577.3</v>
+        <v>534</v>
       </c>
       <c r="I18" t="n">
         <v>545.3952043703589</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>8.970000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="L18" t="n">
         <v>3.42</v>
@@ -1467,7 +1682,7 @@
         <v>0.85</v>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>5.85</v>
       </c>
       <c r="O18" t="n">
         <v>4.2</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>12.18</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44960.55208333334</v>
+        <v>44963.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>529.9</v>
+        <v>560.05</v>
       </c>
       <c r="I19" t="n">
         <v>554.2029632397005</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K19" t="n">
-        <v>0.77</v>
+        <v>-4.88</v>
       </c>
       <c r="L19" t="n">
         <v>8.34</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5</v>
+        <v>4.93</v>
       </c>
       <c r="N19" t="n">
-        <v>4.53</v>
+        <v>5.03</v>
       </c>
       <c r="O19" t="n">
         <v>-5.85</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.93</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44979.38541666666</v>
+        <v>44979.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>613.05</v>
+        <v>606.85</v>
       </c>
       <c r="I20" t="n">
         <v>610.8837041357494</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>9.460000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L20" t="n">
         <v>2.74</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.6</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45006.55208333334</v>
+        <v>45007.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>583</v>
+        <v>615.6</v>
       </c>
       <c r="I21" t="n">
         <v>600.622145234199</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>3.93</v>
+        <v>-1.44</v>
       </c>
       <c r="L21" t="n">
         <v>7.95</v>
@@ -1638,7 +1889,7 @@
         <v>2.54</v>
       </c>
       <c r="N21" t="n">
-        <v>4.26</v>
+        <v>7.29</v>
       </c>
       <c r="O21" t="n">
         <v>-2.65</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.18</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45117.38541666666</v>
+        <v>45117.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>830.35</v>
+        <v>820</v>
       </c>
       <c r="I22" t="n">
         <v>827.618695250528</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>110</v>
+        <v>110.1666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>34.88</v>
+        <v>33.2</v>
       </c>
       <c r="L22" t="n">
         <v>4.78</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.79</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45124.38541666666</v>
+        <v>45124.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>861.1</v>
+        <v>862.7</v>
       </c>
       <c r="I23" t="n">
         <v>862.1495670888344</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.01</v>
+        <v>-5.21</v>
       </c>
       <c r="L23" t="n">
         <v>5.8</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>6.31</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45131.55208333334</v>
+        <v>45132.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>810</v>
+        <v>782.3</v>
       </c>
       <c r="I24" t="n">
         <v>808.2712571950617</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.11</v>
+        <v>-9.32</v>
       </c>
       <c r="L24" t="n">
-        <v>7.73</v>
+        <v>12.83</v>
       </c>
       <c r="M24" t="n">
         <v>0.34</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>10.59</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>795.5</v>
+        <v>846</v>
       </c>
       <c r="I25" t="n">
         <v>823.7928192024301</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.69</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>4.93</v>
+        <v>13.47</v>
       </c>
       <c r="M25" t="n">
-        <v>2.25</v>
+        <v>8.74</v>
       </c>
       <c r="N25" t="n">
-        <v>5.06</v>
+        <v>6.96</v>
       </c>
       <c r="O25" t="n">
         <v>-2.59</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>7.4</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45167.38541666666</v>
+        <v>45167.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>860.25</v>
+        <v>853.5</v>
       </c>
       <c r="I26" t="n">
         <v>857.1809731082168</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>1.68</v>
+        <v>0.89</v>
       </c>
       <c r="L26" t="n">
         <v>2.48</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45177.38541666666</v>
+        <v>45177.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>890.8</v>
+        <v>906.1</v>
       </c>
       <c r="I27" t="n">
         <v>904.6457141328241</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.37</v>
+        <v>-6.16</v>
       </c>
       <c r="L27" t="n">
-        <v>5.79</v>
+        <v>7.73</v>
       </c>
       <c r="M27" t="n">
         <v>1.29</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>6.38</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>866</v>
+        <v>835.4</v>
       </c>
       <c r="I28" t="n">
         <v>853.1744200401571</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.43</v>
+        <v>-7.8</v>
       </c>
       <c r="L28" t="n">
-        <v>5.66</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>-0</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>10.6</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45204.38541666666</v>
+        <v>45204.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>871.35</v>
+        <v>898.5</v>
       </c>
       <c r="I29" t="n">
         <v>895.3348625893843</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.3</v>
+        <v>-7.55</v>
       </c>
       <c r="L29" t="n">
-        <v>7.28</v>
+        <v>7.97</v>
       </c>
       <c r="M29" t="n">
         <v>1.19</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.72</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>920</v>
+        <v>905.45</v>
       </c>
       <c r="I30" t="n">
         <v>918.9140504776675</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>18</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>2.39</v>
+        <v>0.77</v>
       </c>
       <c r="L30" t="n">
         <v>3.12</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.89</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>653.2</v>
+        <v>672.65</v>
       </c>
       <c r="I31" t="n">
         <v>662.202720752811</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K31" t="n">
-        <v>27.86</v>
+        <v>25.71</v>
       </c>
       <c r="L31" t="n">
         <v>5.21</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>7.11</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45322.55208333334</v>
+        <v>45323.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>761</v>
+        <v>609</v>
       </c>
       <c r="I32" t="n">
         <v>721.6965116915325</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K32" t="n">
-        <v>13.13</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>3.61</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>0.54</v>
+        <v>19.97</v>
       </c>
       <c r="N32" t="n">
-        <v>3.96</v>
+        <v>19.97</v>
       </c>
       <c r="O32" t="n">
         <v>2.69</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>14.92</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45342.55208333334</v>
+        <v>45343.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>376.25</v>
+        <v>395.05</v>
       </c>
       <c r="I33" t="n">
         <v>392.4789691230098</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>38.22</v>
+        <v>35.13</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>12.48</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>387</v>
+        <v>369.4</v>
       </c>
       <c r="I34" t="n">
         <v>386.4754660730195</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.04</v>
+        <v>-6.49</v>
       </c>
       <c r="L34" t="n">
-        <v>3.66</v>
+        <v>6.49</v>
       </c>
       <c r="M34" t="n">
         <v>2.76</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>15.33</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45366.55208333334</v>
+        <v>45369.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>370.7</v>
+        <v>389.2</v>
       </c>
       <c r="I35" t="n">
         <v>387.6451518747917</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.35</v>
+        <v>-5.36</v>
       </c>
       <c r="L35" t="n">
         <v>5.89</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>12.87</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>391.8</v>
+        <v>388.75</v>
       </c>
       <c r="I36" t="n">
         <v>391.4320381232096</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K36" t="n">
-        <v>0.67</v>
+        <v>-0.12</v>
       </c>
       <c r="L36" t="n">
         <v>4.15</v>
       </c>
       <c r="M36" t="n">
-        <v>1.11</v>
+        <v>2.76</v>
       </c>
       <c r="N36" t="n">
         <v>2.05</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.69</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45421.55208333334</v>
+        <v>45422.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>333</v>
+        <v>349.65</v>
       </c>
       <c r="I37" t="n">
         <v>346.4608624681679</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>14.34</v>
+        <v>10.06</v>
       </c>
       <c r="L37" t="n">
         <v>5.21</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>10.41</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45447.55208333334</v>
+        <v>45448.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>357.4</v>
+        <v>343.5</v>
       </c>
       <c r="I38" t="n">
         <v>347.4940190032716</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K38" t="n">
-        <v>2.22</v>
+        <v>-1.76</v>
       </c>
       <c r="L38" t="n">
         <v>5.15</v>
       </c>
       <c r="M38" t="n">
-        <v>1.13</v>
+        <v>1.72</v>
       </c>
       <c r="N38" t="n">
         <v>4.9</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>11.77</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>347.5</v>
+        <v>381.3</v>
       </c>
       <c r="I39" t="n">
         <v>377.6511177189747</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.16</v>
+        <v>-11</v>
       </c>
       <c r="L39" t="n">
-        <v>3.25</v>
+        <v>11</v>
       </c>
       <c r="M39" t="n">
         <v>1.47</v>
       </c>
       <c r="N39" t="n">
-        <v>2.21</v>
+        <v>9.73</v>
       </c>
       <c r="O39" t="n">
         <v>-4.87</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>14.82</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>693</v>
+        <v>649.8</v>
       </c>
       <c r="I40" t="n">
         <v>655.1677150937751</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>119.1666666666667</v>
+        <v>122</v>
       </c>
       <c r="K40" t="n">
-        <v>81.75</v>
+        <v>70.42</v>
       </c>
       <c r="L40" t="n">
         <v>8.94</v>
@@ -2721,7 +3200,7 @@
         <v>3.43</v>
       </c>
       <c r="N40" t="n">
-        <v>5.04</v>
+        <v>5.77</v>
       </c>
       <c r="O40" t="n">
         <v>9.73</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>19.08</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45573.38541666666</v>
+        <v>45573.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>716.6</v>
+        <v>752.65</v>
       </c>
       <c r="I41" t="n">
         <v>736.9086975478491</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-10.28</v>
+        <v>-15.83</v>
       </c>
       <c r="L41" t="n">
-        <v>11.4</v>
+        <v>18.94</v>
       </c>
       <c r="M41" t="n">
         <v>1.25</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>15.69</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>788</v>
+        <v>757.4</v>
       </c>
       <c r="I42" t="n">
         <v>773.8450822370203</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K42" t="n">
-        <v>4.7</v>
+        <v>0.63</v>
       </c>
       <c r="L42" t="n">
         <v>11.01</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>12.85</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45617.38541666666</v>
+        <v>45617.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>827.6</v>
+        <v>843</v>
       </c>
       <c r="I43" t="n">
         <v>842.3448549508757</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>-9.27</v>
+        <v>-11.3</v>
       </c>
       <c r="L43" t="n">
-        <v>10.36</v>
+        <v>12.62</v>
       </c>
       <c r="M43" t="n">
         <v>1.5</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.03</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>982</v>
+        <v>913.25</v>
       </c>
       <c r="I44" t="n">
         <v>949.0813556298544</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K44" t="n">
-        <v>16.49</v>
+        <v>8.33</v>
       </c>
       <c r="L44" t="n">
         <v>1.9</v>
@@ -2949,7 +3476,7 @@
         <v>1.88</v>
       </c>
       <c r="N44" t="n">
-        <v>4.12</v>
+        <v>7.85</v>
       </c>
       <c r="O44" t="n">
         <v>3.88</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>12.82</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>855</v>
+        <v>901.9</v>
       </c>
       <c r="I45" t="n">
         <v>879.90828173875</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>6.38</v>
+        <v>1.24</v>
       </c>
       <c r="L45" t="n">
         <v>8.1</v>
       </c>
       <c r="M45" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.81</v>
       </c>
       <c r="N45" t="n">
-        <v>4.42</v>
+        <v>5.08</v>
       </c>
       <c r="O45" t="n">
         <v>-7.85</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>11.9</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45681.38541666666</v>
+        <v>45681.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>817</v>
+        <v>804.9</v>
       </c>
       <c r="I46" t="n">
         <v>810.5951949882638</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K46" t="n">
-        <v>-9.41</v>
+        <v>-10.76</v>
       </c>
       <c r="L46" t="n">
         <v>14.29</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>13.24</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45734.38541666666</v>
+        <v>45734.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>727.3</v>
+        <v>741.65</v>
       </c>
       <c r="I47" t="n">
         <v>733.4657985185935</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>52.83333333333334</v>
+        <v>53</v>
       </c>
       <c r="K47" t="n">
-        <v>9.640000000000001</v>
+        <v>7.86</v>
       </c>
       <c r="L47" t="n">
         <v>2.35</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.61</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>861.4</v>
+        <v>830.1</v>
       </c>
       <c r="I48" t="n">
         <v>845.8148872480002</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>43</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K48" t="n">
-        <v>16.15</v>
+        <v>11.93</v>
       </c>
       <c r="L48" t="n">
         <v>3.16</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>11.44</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45806.55208333334</v>
+        <v>45807.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>880</v>
+        <v>890.25</v>
       </c>
       <c r="I49" t="n">
         <v>882.1183008588628</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.01</v>
+        <v>-7.25</v>
       </c>
       <c r="L49" t="n">
-        <v>7.51</v>
+        <v>7.86</v>
       </c>
       <c r="M49" t="n">
         <v>3.96</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.78</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45819.55208333334</v>
+        <v>45820.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>959.55</v>
+        <v>906.65</v>
       </c>
       <c r="I50" t="n">
         <v>917.6350872344198</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K50" t="n">
-        <v>7.78</v>
+        <v>1.84</v>
       </c>
       <c r="L50" t="n">
-        <v>1.15</v>
+        <v>2.9</v>
       </c>
       <c r="M50" t="n">
-        <v>0.12</v>
+        <v>4.85</v>
       </c>
       <c r="N50" t="n">
-        <v>0.76</v>
+        <v>6.94</v>
       </c>
       <c r="O50" t="n">
         <v>1.14</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>6.03</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45839.38541666666</v>
+        <v>45839.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>928.9</v>
+        <v>929.9</v>
       </c>
       <c r="I51" t="n">
         <v>929.5514996756834</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.45</v>
+        <v>-2.56</v>
       </c>
       <c r="L51" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="M51" t="n">
         <v>1.34</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.02</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45919.38541666666</v>
+        <v>45919.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1217.5</v>
+        <v>1173.8</v>
       </c>
       <c r="I52" t="n">
         <v>1216.781912681</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>79.83333333333333</v>
+        <v>80</v>
       </c>
       <c r="K52" t="n">
-        <v>30.93</v>
+        <v>26.23</v>
       </c>
       <c r="L52" t="n">
         <v>3.63</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.84</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1164.9</v>
+        <v>1221.4</v>
       </c>
       <c r="I53" t="n">
         <v>1180.228160864044</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>0.76</v>
+        <v>-4.06</v>
       </c>
       <c r="L53" t="n">
-        <v>3.78</v>
+        <v>4.11</v>
       </c>
       <c r="M53" t="n">
         <v>0.74</v>
       </c>
       <c r="N53" t="n">
-        <v>2.26</v>
+        <v>5.1</v>
       </c>
       <c r="O53" t="n">
         <v>-4.57</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1283</v>
+        <v>1267.9</v>
       </c>
       <c r="I54" t="n">
         <v>1273.650206333705</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K54" t="n">
-        <v>5.04</v>
+        <v>3.81</v>
       </c>
       <c r="L54" t="n">
         <v>5.02</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>5.5</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45988.55208333334</v>
+        <v>45989.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1293</v>
+        <v>1331.2</v>
       </c>
       <c r="I55" t="n">
         <v>1306.607913448656</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.98</v>
+        <v>-4.99</v>
       </c>
       <c r="L55" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="M55" t="n">
         <v>1.32</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>6.16</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46000.55208333334</v>
+        <v>46001.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1317</v>
+        <v>1284.6</v>
       </c>
       <c r="I56" t="n">
         <v>1296.868438877702</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.07</v>
+        <v>-3.5</v>
       </c>
       <c r="L56" t="n">
-        <v>3.2</v>
+        <v>4.52</v>
       </c>
       <c r="M56" t="n">
         <v>0.74</v>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>3.88</v>
       </c>
       <c r="O56" t="n">
         <v>2.09</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.83</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46010.38541666666</v>
+        <v>46010.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>1310.5</v>
+        <v>1334.8</v>
       </c>
       <c r="I57" t="n">
         <v>1332.972969656268</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.02</v>
+        <v>-3.91</v>
       </c>
       <c r="L57" t="n">
-        <v>2.61</v>
+        <v>4.7</v>
       </c>
       <c r="M57" t="n">
         <v>0.9399999999999999</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.02</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1292</v>
+        <v>1262.5</v>
       </c>
       <c r="I58" t="n">
         <v>1290.091372532115</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.21</v>
+        <v>-5.42</v>
       </c>
       <c r="L58" t="n">
-        <v>3.95</v>
+        <v>6.5</v>
       </c>
       <c r="M58" t="n">
         <v>0.61</v>
       </c>
       <c r="N58" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="O58" t="n">
         <v>3.68</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.74</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46036.55208333334</v>
+        <v>46038.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1308</v>
+        <v>1345.5</v>
       </c>
       <c r="I59" t="n">
         <v>1333.787556697636</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.6</v>
+        <v>-6.57</v>
       </c>
       <c r="L59" t="n">
-        <v>4.74</v>
+        <v>7.23</v>
       </c>
       <c r="M59" t="n">
         <v>0.83</v>
       </c>
       <c r="N59" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="O59" t="n">
         <v>-1.83</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>6.68</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46042.55208333334</v>
+        <v>46043.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1300</v>
+        <v>1244.9</v>
       </c>
       <c r="I60" t="n">
         <v>1270.443501481052</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.38</v>
+        <v>-7.48</v>
       </c>
       <c r="L60" t="n">
-        <v>4.22</v>
+        <v>9.1</v>
       </c>
       <c r="M60" t="n">
-        <v>0.29</v>
+        <v>0.46</v>
       </c>
       <c r="N60" t="n">
-        <v>2.59</v>
+        <v>5.21</v>
       </c>
       <c r="O60" t="n">
         <v>2.45</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.82</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46071.38541666666</v>
+        <v>46071.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>1191.8</v>
+        <v>1200</v>
       </c>
       <c r="I61" t="n">
         <v>1198.32021978759</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K61" t="n">
-        <v>4.27</v>
+        <v>3.61</v>
       </c>
       <c r="L61" t="n">
         <v>4.73</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>6.97</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46079.55208333334</v>
+        <v>46080.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1123</v>
+        <v>1102.4</v>
       </c>
       <c r="I62" t="n">
         <v>1116.419381917626</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.42</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>8.039999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="M62" t="n">
         <v>0.91</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.33</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46098.55208333334</v>
+        <v>46099.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1020</v>
+        <v>1075.9</v>
       </c>
       <c r="I63" t="n">
         <v>1046.373387554622</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K63" t="n">
-        <v>7.47</v>
+        <v>2.4</v>
       </c>
       <c r="L63" t="n">
         <v>2.73</v>
@@ -4032,7 +4787,7 @@
         <v>0.77</v>
       </c>
       <c r="N63" t="n">
-        <v>3.63</v>
+        <v>5.02</v>
       </c>
       <c r="O63" t="n">
         <v>-2.18</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>9.99</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1050</v>
+        <v>991.7</v>
       </c>
       <c r="I64" t="n">
         <v>1000.094970044584</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.41</v>
+        <v>-7.83</v>
       </c>
       <c r="L64" t="n">
-        <v>4.92</v>
+        <v>7.99</v>
       </c>
       <c r="M64" t="n">
         <v>2.43</v>
       </c>
       <c r="N64" t="n">
-        <v>2.45</v>
+        <v>5.43</v>
       </c>
       <c r="O64" t="n">
         <v>5.02</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>11.12</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1028</v>
+        <v>1104.45</v>
       </c>
       <c r="I65" t="n">
         <v>1047.981754015355</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.66</v>
+        <v>-11.37</v>
       </c>
       <c r="L65" t="n">
-        <v>8</v>
+        <v>11.53</v>
       </c>
       <c r="M65" t="n">
         <v>4.1</v>
       </c>
       <c r="N65" t="n">
-        <v>4.88</v>
+        <v>8.56</v>
       </c>
       <c r="O65" t="n">
         <v>-5.43</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>11.42</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1105</v>
+        <v>1097.3</v>
       </c>
       <c r="I66" t="n">
         <v>1103.742090522255</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K66" t="n">
-        <v>0.05</v>
+        <v>-0.65</v>
       </c>
       <c r="L66" t="n">
         <v>4.83</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>6.81</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1110</v>
+        <v>1171.7</v>
       </c>
       <c r="I67" t="n">
         <v>1167.667690988148</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.16</v>
+        <v>-6.78</v>
       </c>
       <c r="L67" t="n">
-        <v>2.34</v>
+        <v>8.08</v>
       </c>
       <c r="M67" t="n">
-        <v>1.55</v>
+        <v>3.6</v>
       </c>
       <c r="N67" t="n">
-        <v>2.01</v>
+        <v>7.66</v>
       </c>
       <c r="O67" t="n">
         <v>-0.8100000000000001</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1125</v>
+        <v>1091</v>
       </c>
       <c r="I68" t="n">
         <v>1109.145537648408</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.99</v>
+        <v>-6.89</v>
       </c>
       <c r="L68" t="n">
-        <v>5.91</v>
+        <v>7.63</v>
       </c>
       <c r="M68" t="n">
         <v>1.16</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1066</v>
+        <v>1122.7</v>
       </c>
       <c r="I69" t="n">
         <v>1101.109937043582</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K69" t="n">
-        <v>2.29</v>
+        <v>-2.91</v>
       </c>
       <c r="L69" t="n">
         <v>7.42</v>
       </c>
       <c r="M69" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="N69" t="n">
-        <v>4.24</v>
+        <v>5.23</v>
       </c>
       <c r="O69" t="n">
         <v>-1.6</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46224.55208333334</v>
+        <v>46225.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1297.9</v>
+        <v>1278.5</v>
       </c>
       <c r="I70" t="n">
         <v>1289.512975981257</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K70" t="n">
-        <v>15.61</v>
+        <v>13.88</v>
       </c>
       <c r="L70" t="n">
         <v>5.21</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46233.55208333334</v>
+        <v>46234.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>1330.9</v>
+        <v>1353.5</v>
       </c>
       <c r="I71" t="n">
         <v>1351.794264299338</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.1</v>
+        <v>-5.87</v>
       </c>
       <c r="L71" t="n">
-        <v>5.61</v>
+        <v>6.37</v>
       </c>
       <c r="M71" t="n">
         <v>0.39</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>7.52</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46266.38541666666</v>
+        <v>46266.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>1643</v>
+        <v>1627</v>
       </c>
       <c r="I72" t="n">
         <v>1632.479435545086</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K72" t="n">
-        <v>21.39</v>
+        <v>20.21</v>
       </c>
       <c r="L72" t="n">
         <v>2.31</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>6.28</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46273.55208333334</v>
+        <v>46274.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1662</v>
+        <v>1752.6</v>
       </c>
       <c r="I73" t="n">
         <v>1704.329002676076</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>-2.15</v>
+        <v>-7.72</v>
       </c>
       <c r="L73" t="n">
-        <v>4.35</v>
+        <v>7.99</v>
       </c>
       <c r="M73" t="n">
-        <v>0.61</v>
+        <v>0.9</v>
       </c>
       <c r="N73" t="n">
-        <v>1.97</v>
+        <v>5.48</v>
       </c>
       <c r="O73" t="n">
         <v>-3.03</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>7.91</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46289.55208333334</v>
+        <v>46290.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>1734.5</v>
+        <v>1669.8</v>
       </c>
       <c r="I74" t="n">
         <v>1709.898671924327</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.03</v>
+        <v>-4.72</v>
       </c>
       <c r="L74" t="n">
-        <v>4.36</v>
+        <v>4.79</v>
       </c>
       <c r="M74" t="n">
         <v>0.5</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>9.17</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46301.55208333334</v>
+        <v>46302.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>1685</v>
+        <v>1742.6</v>
       </c>
       <c r="I75" t="n">
         <v>1740.168023666482</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.91</v>
+        <v>-4.36</v>
       </c>
       <c r="L75" t="n">
-        <v>4.64</v>
+        <v>6.24</v>
       </c>
       <c r="M75" t="n">
         <v>0.95</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>7.61</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46307.55208333334</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>1659.6</v>
+        <v>1590.9</v>
       </c>
       <c r="I76" t="n">
         <v>1627.432900998463</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.76</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L76" t="n">
         <v>10.55</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,12 @@
       <c r="Q77" t="n">
         <v>20</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6935,7 +7864,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.1</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="6">
@@ -6945,7 +7874,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="7">
@@ -6955,7 +7884,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>119.2</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">
@@ -6965,7 +7894,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -6975,7 +7904,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.2</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="10">
@@ -6985,7 +7914,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46.3</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="11">
@@ -7025,7 +7954,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.52</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="15">
@@ -7035,7 +7964,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.01</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="16">
@@ -7045,7 +7974,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="17">
@@ -7055,7 +7984,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>81.75</v>
+        <v>70.42</v>
       </c>
     </row>
     <row r="18">
@@ -7065,7 +7994,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -7075,7 +8004,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.18</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="20">
@@ -7085,7 +8014,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.78</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="21">
@@ -7095,7 +8024,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.29</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="22">
@@ -7105,7 +8034,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -7115,7 +8044,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -7125,7 +8054,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="25">
@@ -7135,7 +8064,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.26</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="26">
@@ -7145,7 +8074,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.55</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="27">
@@ -7155,7 +8084,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15.26</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="28">
@@ -7165,7 +8094,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
